--- a/Templates/water-quality-analysis/test-template.xlsx
+++ b/Templates/water-quality-analysis/test-template.xlsx
@@ -1026,623 +1026,503 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>BDRK_R0018</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>B01M</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>20260727</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>BDRK_R0016</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>B02H</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>20260727</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>1010</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>BDRK_R0009</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>B03H</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>20260727</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>1020</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>BDRK_R0020</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>B04M</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>20260727</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>1030</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>BDRK_R0019</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>B05H</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>20260727</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>1040</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>BDRK_R0003</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>B06H</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>20260727</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>1050</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>BDRK_R0007</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>B07H</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>20260727</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>1060</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>BDRK_R0013</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>B08M</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>20260727</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>1070</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>BDRK_R0014</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>B09H</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>20260727</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>1080</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>BDRK_R0010</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>B10M</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>20260727</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>1090</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>BDRK_R0005</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>U11H</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>20260727</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>1100</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>BDRK_R0004</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>U12M</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>20260727</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>1110</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>BDRK_R0012</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>U13H</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>20260727</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>1120</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>BDRK_R0017</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>U14H</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>20260727</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>1130</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>BDRK_R0015</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>U15H</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>20260727</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>1140</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>BDRK_R0002</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>U16M</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>20260727</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>1150</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>BDRK_R0011</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>U17H</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>20260727</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>1160</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="B19" t="inlineStr">
         <is>
           <t>BDRK_R0001</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>BDRK_U14H_GB_____________</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>U14H</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>20260823</v>
-      </c>
-      <c r="G2">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>BDRK_R0002</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>BDRK_B07H_GB_____________</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>B07H</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E3">
-        <v>2</v>
-      </c>
-      <c r="F3">
-        <v>20260823</v>
-      </c>
-      <c r="G3">
-        <v>1700</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>BDRK_R0003</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>BDRK_U19M_GB_____________</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>U18H</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>20260727</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>1170</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>BDRK_R0008</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
         <is>
           <t>U19M</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E4">
-        <v>3</v>
-      </c>
-      <c r="F4">
-        <v>20260823</v>
-      </c>
-      <c r="G4">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>BDRK_R0004</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>BDRK_B09H_GB_____________</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>B09H</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E5">
-        <v>4</v>
-      </c>
-      <c r="F5">
-        <v>20260823</v>
-      </c>
-      <c r="G5">
-        <v>1900</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>BDRK_R0005</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>BDRK_B02H_GB_____________</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>B02H</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E6">
-        <v>5</v>
-      </c>
-      <c r="F6">
-        <v>20260823</v>
-      </c>
-      <c r="G6">
-        <v>830</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>20260727</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>1180</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="B21" t="inlineStr">
         <is>
           <t>BDRK_R0006</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>BDRK_U13H_GB_____________</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>U13H</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E7">
-        <v>6</v>
-      </c>
-      <c r="F7">
-        <v>20260823</v>
-      </c>
-      <c r="G7">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>BDRK_R0007</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>BDRK_B03H_GB_____________</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>B03H</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E8">
-        <v>7</v>
-      </c>
-      <c r="F8">
-        <v>20260823</v>
-      </c>
-      <c r="G8">
-        <v>900</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>BDRK_R0008</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>BDRK_U15H_GB_____________</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>U15H</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E9">
-        <v>8</v>
-      </c>
-      <c r="F9">
-        <v>20260823</v>
-      </c>
-      <c r="G9">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>BDRK_R0009</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>BDRK_U12M_GB_____________</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>U12M</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E10">
-        <v>9</v>
-      </c>
-      <c r="F10">
-        <v>20260823</v>
-      </c>
-      <c r="G10">
-        <v>900</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>BDRK_R0010</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>BDRK_U18H_GB_____________</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>U18H</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E11">
-        <v>10</v>
-      </c>
-      <c r="F11">
-        <v>20260823</v>
-      </c>
-      <c r="G11">
-        <v>1900</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>BDRK_R0011</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>BDRK_B08M_GB_____________</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>B08M</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E12">
-        <v>11</v>
-      </c>
-      <c r="F12">
-        <v>20260823</v>
-      </c>
-      <c r="G12">
-        <v>1800</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>BDRK_R0012</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>BDRK_U16M_GB_____________</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>U16M</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E13">
-        <v>12</v>
-      </c>
-      <c r="F13">
-        <v>20260823</v>
-      </c>
-      <c r="G13">
-        <v>1700</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>BDRK_R0013</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>BDRK_C20M_GB_____________</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>C20M</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E14">
-        <v>13</v>
-      </c>
-      <c r="F14">
-        <v>20260823</v>
-      </c>
-      <c r="G14">
-        <v>2100</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>BDRK_R0014</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>BDRK_B10M_GB_____________</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>B10M</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E15">
-        <v>14</v>
-      </c>
-      <c r="F15">
-        <v>20260823</v>
-      </c>
-      <c r="G15">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>BDRK_R0015</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>BDRK_B06H_GB_____________</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>B06H</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E16">
-        <v>15</v>
-      </c>
-      <c r="F16">
-        <v>20260823</v>
-      </c>
-      <c r="G16">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>BDRK_R0016</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>BDRK_B01M_GB_____________</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>B01M</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E17">
-        <v>16</v>
-      </c>
-      <c r="F17">
-        <v>20260823</v>
-      </c>
-      <c r="G17">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>BDRK_R0017</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>BDRK_B04M_GB_____________</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>B04M</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E18">
-        <v>17</v>
-      </c>
-      <c r="F18">
-        <v>20260823</v>
-      </c>
-      <c r="G18">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>BDRK_R0018</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>BDRK_U17H_GB_____________</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>U17H</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E19">
-        <v>18</v>
-      </c>
-      <c r="F19">
-        <v>20260823</v>
-      </c>
-      <c r="G19">
-        <v>1800</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>BDRK_R0019</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>BDRK_U11H_GB_____________</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>U11H</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E20">
-        <v>19</v>
-      </c>
-      <c r="F20">
-        <v>20260823</v>
-      </c>
-      <c r="G20">
-        <v>830</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>BDRK_R0020</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>BDRK_B05H_GB_____________</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>B05H</t>
-        </is>
-      </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E21">
-        <v>20</v>
-      </c>
-      <c r="F21">
-        <v>20260823</v>
-      </c>
-      <c r="G21">
-        <v>1200</v>
+          <t>20260727</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>1190</t>
+        </is>
       </c>
     </row>
   </sheetData>
